--- a/McLennan-Community-College/_MCCSVA/SVA is back at MCC.xlsx
+++ b/McLennan-Community-College/_MCCSVA/SVA is back at MCC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d62837459e03f1f2/Documents/Github-Repo-for-Schools/McLennan-Community-College/_MCCSVA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1976FA18-08DA-4F4F-B1C4-55DE0B624DAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{DCA258C4-D519-4D94-824A-AD11FC51C8A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E1C1495-77B2-46A2-B134-31AD6BE23F04}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="48">
   <si>
     <t>Id</t>
   </si>
@@ -144,13 +144,49 @@
   </si>
   <si>
     <t xml:space="preserve">Career fair (maybe get Hiring Our Heroes to come here), a bbq, and a service project to help out our community </t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Gresham </t>
+  </si>
+  <si>
+    <t>Jg0599584@students.mclennan.edu</t>
+  </si>
+  <si>
+    <t>Chapter Member</t>
+  </si>
+  <si>
+    <t>Vice President: To handle recruitment and help build our numbers.;President: To handle the overall operations of the chapter.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limited club activities </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A BBQ would be great </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Brandon</t>
+  </si>
+  <si>
+    <t>Garciabrandon560@yahoo.com</t>
+  </si>
+  <si>
+    <t>Student Life Center (SLC)</t>
+  </si>
+  <si>
+    <t>Secretary: To keep us organized and handle communication.;Vice President: To handle recruitment and help build our numbers.</t>
+  </si>
+  <si>
+    <t>Lack of communication, initiative on task, effort, and proper planning.</t>
+  </si>
+  <si>
+    <t>Group meetings, hiking nearby trails, bbq</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -179,11 +215,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -260,8 +298,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:X2" totalsRowShown="0">
-  <autoFilter ref="A1:X2" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:X4" totalsRowShown="0">
+  <autoFilter ref="A1:X4" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="24">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="18">
       <extLst>
@@ -435,7 +473,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="UPu8BEDlaUOJdWKeGbZfVucHO0L4GgtCgdyeaFjSGWhUMk8zNVhFSFlJNlhMWllFREJJSzNUNzNUMC4u" isFormConnected="1" maxResponseId="2" latestEventMarker="0">
+      <xlmsforms:msForm id="UPu8BEDlaUOJdWKeGbZfVucHO0L4GgtCgdyeaFjSGWhUMk8zNVhFSFlJNlhMWllFREJJSzNUNzNUMC4u" maxResponseId="4" latestEventMarker="2">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -764,8 +802,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:X4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
@@ -774,7 +812,7 @@
     <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="33.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="34.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="31.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="37.5703125" bestFit="1" customWidth="1"/>
@@ -793,7 +831,7 @@
     <col min="24" max="24" width="122" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -867,7 +905,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2</v>
       </c>
@@ -922,6 +960,128 @@
       <c r="W2" s="1">
         <v>46073</v>
       </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3">
+        <v>46058.467824074098</v>
+      </c>
+      <c r="C3" s="3">
+        <v>46058.4696527778</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="5">
+        <v>2545382134</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L3" s="5">
+        <v>599584</v>
+      </c>
+      <c r="M3" s="5">
+        <v>2027</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="U3" s="1">
+        <v>46059</v>
+      </c>
+      <c r="V3" s="1">
+        <v>46062</v>
+      </c>
+      <c r="W3" s="1">
+        <v>46062</v>
+      </c>
+      <c r="X3" s="4"/>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3">
+        <v>46065.341400463003</v>
+      </c>
+      <c r="C4" s="3">
+        <v>46065.343761574099</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G4" s="5">
+        <v>2542521534</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="5">
+        <v>585939</v>
+      </c>
+      <c r="M4" s="5">
+        <v>2028</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="T4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="U4" s="1">
+        <v>46071</v>
+      </c>
+      <c r="V4" s="1">
+        <v>46070</v>
+      </c>
+      <c r="W4" s="1">
+        <v>46069</v>
+      </c>
+      <c r="X4" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
